--- a/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46127.4980739234</v>
+        <v>46131.49812913174</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46131.49812913174</v>
+        <v>46132.49807135435</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>

--- a/zone_struktura_zrodel_ciepla_polska.xlsx
+++ b/zone_struktura_zrodel_ciepla_polska.xlsx
@@ -542,7 +542,7 @@
       <c r="D15" s="8" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="9">
-        <v>46132.49807135435</v>
+        <v>46134.4980754978</v>
       </c>
       <c r="G15" s="9" t="inlineStr"/>
     </row>
